--- a/data/trans_orig/P1413-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1413-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor de espalda en 2007</t>
+          <t>Población con diagnóstico de dolor de espalda, cuello, hombro, cintura (cervical/lumbar) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51683</t>
+          <t>52942</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>82027</t>
+          <t>84492</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28543</t>
+          <t>29287</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52087</t>
+          <t>53726</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>86803</t>
+          <t>87324</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>126993</t>
+          <t>126834</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>391749</t>
+          <t>389284</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>422093</t>
+          <t>420834</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>254593</t>
+          <t>252954</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>278137</t>
+          <t>277393</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>653464</t>
+          <t>653623</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>693654</t>
+          <t>693133</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,81%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25857</t>
+          <t>27147</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50223</t>
+          <t>49946</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48694</t>
+          <t>49180</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78096</t>
+          <t>77671</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>82855</t>
+          <t>82598</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>118911</t>
+          <t>119688</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>316711</t>
+          <t>316988</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>341077</t>
+          <t>339787</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>293769</t>
+          <t>294194</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>323171</t>
+          <t>322685</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>619888</t>
+          <t>619111</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>655944</t>
+          <t>656201</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,82%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85234</t>
+          <t>84706</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>122049</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25907</t>
+          <t>26337</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45852</t>
+          <t>48241</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>116941</t>
+          <t>116220</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159684</t>
+          <t>157461</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,17%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>422204</t>
+          <t>420340</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>457155</t>
+          <t>457683</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>121930</t>
+          <t>119541</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>141875</t>
+          <t>141445</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>550487</t>
+          <t>552710</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>593230</t>
+          <t>593951</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,63%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>226308</t>
+          <t>223906</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>285228</t>
+          <t>282438</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>117324</t>
+          <t>116810</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>158861</t>
+          <t>160424</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>357144</t>
+          <t>355575</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>428054</t>
+          <t>426062</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,82%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>953106</t>
+          <t>955896</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1012026</t>
+          <t>1014428</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>555424</t>
+          <t>553861</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>596961</t>
+          <t>597475</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1524566</t>
+          <t>1526558</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1595476</t>
+          <t>1597045</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,79%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53379</t>
+          <t>54348</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83066</t>
+          <t>82625</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>103452</t>
+          <t>103514</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>144563</t>
+          <t>142743</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>164471</t>
+          <t>165954</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>214197</t>
+          <t>216235</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>267489</t>
+          <t>267930</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>297176</t>
+          <t>296207</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>424189</t>
+          <t>426009</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>465300</t>
+          <t>465238</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>705110</t>
+          <t>703072</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>754836</t>
+          <t>753353</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,95%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12082</t>
+          <t>11384</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>226778</t>
+          <t>227550</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>284260</t>
+          <t>282573</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>232843</t>
+          <t>230949</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>288537</t>
+          <t>289298</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,7%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>286119</t>
+          <t>286817</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>295641</t>
+          <t>296248</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>964500</t>
+          <t>966187</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1021982</t>
+          <t>1021210</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1258423</t>
+          <t>1257662</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1314117</t>
+          <t>1316011</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,07%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>488533</t>
+          <t>490166</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>571906</t>
+          <t>574085</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>604949</t>
+          <t>605538</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>698768</t>
+          <t>698028</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1122737</t>
+          <t>1115607</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1246389</t>
+          <t>1243162</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,7%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2698284</t>
+          <t>2696105</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2781657</t>
+          <t>2780024</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2679356</t>
+          <t>2680096</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2773175</t>
+          <t>2772586</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5401925</t>
+          <t>5405152</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5525577</t>
+          <t>5532707</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,22%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor de espalda en 2012</t>
+          <t>Población con diagnóstico de dolor de espalda, cuello, hombro, cintura (cervical/lumbar) en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21880</t>
+          <t>20704</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43036</t>
+          <t>42062</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27957</t>
+          <t>28784</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52958</t>
+          <t>54608</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55183</t>
+          <t>54353</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86789</t>
+          <t>89795</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>394175</t>
+          <t>395149</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>415331</t>
+          <t>416507</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>261496</t>
+          <t>259846</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286497</t>
+          <t>285670</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>664876</t>
+          <t>661870</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>696482</t>
+          <t>697312</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24236</t>
+          <t>24450</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48868</t>
+          <t>48471</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36354</t>
+          <t>35522</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62997</t>
+          <t>61772</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65662</t>
+          <t>66457</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>101107</t>
+          <t>102352</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>369929</t>
+          <t>370326</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>394561</t>
+          <t>394347</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>275014</t>
+          <t>276239</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>301657</t>
+          <t>302489</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>655701</t>
+          <t>654456</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>691146</t>
+          <t>690351</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,22%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49025</t>
+          <t>48978</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82145</t>
+          <t>81961</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29033</t>
+          <t>28702</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53025</t>
+          <t>52547</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85777</t>
+          <t>86219</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>129168</t>
+          <t>124834</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>547270</t>
+          <t>547454</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>580390</t>
+          <t>580437</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>207104</t>
+          <t>207582</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>231096</t>
+          <t>231427</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>760376</t>
+          <t>764710</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>803767</t>
+          <t>803325</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,31%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>108099</t>
+          <t>107709</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>149196</t>
+          <t>151895</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>103861</t>
+          <t>104239</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>146132</t>
+          <t>146747</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>223740</t>
+          <t>224667</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>284936</t>
+          <t>283065</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1009813</t>
+          <t>1007114</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1050910</t>
+          <t>1051300</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>618590</t>
+          <t>617975</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>660861</t>
+          <t>660483</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1638795</t>
+          <t>1640666</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1699991</t>
+          <t>1699064</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,32%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31997</t>
+          <t>32852</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58203</t>
+          <t>58083</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>154581</t>
+          <t>154608</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>200266</t>
+          <t>201518</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>193639</t>
+          <t>192124</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>247772</t>
+          <t>248801</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>452393</t>
+          <t>452513</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>478599</t>
+          <t>477744</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>559980</t>
+          <t>558728</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>605665</t>
+          <t>605638</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1023071</t>
+          <t>1022042</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1077204</t>
+          <t>1078719</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,88%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13893</t>
+          <t>14426</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>191105</t>
+          <t>190323</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>244488</t>
+          <t>244135</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>194108</t>
+          <t>193149</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>252225</t>
+          <t>250311</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252989</t>
+          <t>252456</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264851</t>
+          <t>264830</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>864863</t>
+          <t>865216</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>918246</t>
+          <t>919028</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1124008</t>
+          <t>1125922</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1182125</t>
+          <t>1183084</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,97%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>273282</t>
+          <t>275438</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>346383</t>
+          <t>344249</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>596647</t>
+          <t>601542</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>688257</t>
+          <t>688971</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>894787</t>
+          <t>891995</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1011430</t>
+          <t>1010933</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3075527</t>
+          <t>3077661</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3148628</t>
+          <t>3146472</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2858658</t>
+          <t>2857944</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2950268</t>
+          <t>2945373</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5957395</t>
+          <t>5957892</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6074038</t>
+          <t>6076830</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,2%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor de espalda en 2016</t>
+          <t>Población con diagnóstico de dolor de espalda, cuello, hombro, cintura (cervical/lumbar) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22175</t>
+          <t>23580</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47438</t>
+          <t>46263</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18149</t>
+          <t>17459</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38913</t>
+          <t>38084</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45632</t>
+          <t>46501</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>77514</t>
+          <t>79158</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>381654</t>
+          <t>382829</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>406917</t>
+          <t>405512</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>308142</t>
+          <t>308971</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>328906</t>
+          <t>329596</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>698633</t>
+          <t>696989</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>730515</t>
+          <t>729646</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,01%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13155</t>
+          <t>13267</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32889</t>
+          <t>33392</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32481</t>
+          <t>33249</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57679</t>
+          <t>57877</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51084</t>
+          <t>50385</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83208</t>
+          <t>81932</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>344338</t>
+          <t>343835</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>364072</t>
+          <t>363960</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>314594</t>
+          <t>314396</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>339792</t>
+          <t>339024</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>666292</t>
+          <t>667568</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>698416</t>
+          <t>699115</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,28%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29801</t>
+          <t>29816</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54747</t>
+          <t>54571</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25330</t>
+          <t>24790</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47220</t>
+          <t>45526</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59737</t>
+          <t>60415</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93256</t>
+          <t>93979</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,66%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>467167</t>
+          <t>467343</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>492113</t>
+          <t>492098</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>118903</t>
+          <t>120597</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>140793</t>
+          <t>141333</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>594780</t>
+          <t>594057</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>628299</t>
+          <t>627621</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,22%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86646</t>
+          <t>86716</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128695</t>
+          <t>124337</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88409</t>
+          <t>86148</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>126759</t>
+          <t>127419</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>186370</t>
+          <t>185482</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>240514</t>
+          <t>242337</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1020943</t>
+          <t>1025301</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1062992</t>
+          <t>1062922</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>699117</t>
+          <t>698457</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>737467</t>
+          <t>739728</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1735000</t>
+          <t>1733177</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1789144</t>
+          <t>1790032</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,61%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>58714</t>
+          <t>59686</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>91987</t>
+          <t>91494</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>107015</t>
+          <t>107734</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>149352</t>
+          <t>148837</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>177976</t>
+          <t>174490</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>228445</t>
+          <t>226375</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>528719</t>
+          <t>529212</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>561992</t>
+          <t>561020</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>588892</t>
+          <t>589407</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>631229</t>
+          <t>630510</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1130505</t>
+          <t>1132575</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1180974</t>
+          <t>1184460</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>87,16%</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>126884</t>
+          <t>126112</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>173781</t>
+          <t>173183</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>127987</t>
+          <t>129175</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>179983</t>
+          <t>178157</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>281445</t>
+          <t>280714</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>908244</t>
+          <t>908842</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>955141</t>
+          <t>955913</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1189187</t>
+          <t>1191013</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1241183</t>
+          <t>1239995</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,57%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>247397</t>
+          <t>247317</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>312740</t>
+          <t>312925</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>448731</t>
+          <t>444384</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>534554</t>
+          <t>535674</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>710537</t>
+          <t>710125</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>820487</t>
+          <t>823016</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3072982</t>
+          <t>3072797</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3138325</t>
+          <t>3138405</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2997042</t>
+          <t>2995922</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3082865</t>
+          <t>3087212</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6096831</t>
+          <t>6094302</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6206781</t>
+          <t>6207193</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de dolor de espalda en 2023</t>
+          <t>Población con diagnóstico de dolor de espalda, cuello, hombro, cintura (cervical/lumbar) en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>59120</t>
+          <t>59846</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89210</t>
+          <t>89794</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>88820</t>
+          <t>90272</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>121416</t>
+          <t>121078</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>155684</t>
+          <t>155400</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>199795</t>
+          <t>198407</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>414889</t>
+          <t>414305</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>444979</t>
+          <t>444253</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>325406</t>
+          <t>325744</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>358002</t>
+          <t>356550</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>751125</t>
+          <t>752513</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>795236</t>
+          <t>795520</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,66%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60318</t>
+          <t>62073</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91125</t>
+          <t>91770</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>90208</t>
+          <t>89524</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>120018</t>
+          <t>119174</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>159053</t>
+          <t>159001</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>205203</t>
+          <t>202684</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>360328</t>
+          <t>359683</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>391135</t>
+          <t>389380</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>261893</t>
+          <t>262737</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>291703</t>
+          <t>292387</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>628161</t>
+          <t>630680</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>674311</t>
+          <t>674363</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,92%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36292</t>
+          <t>36674</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>154232</t>
+          <t>156361</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51661</t>
+          <t>51270</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71379</t>
+          <t>69973</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64146</t>
+          <t>72349</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>224981</t>
+          <t>225099</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,98%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>513313</t>
+          <t>511184</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>631253</t>
+          <t>630871</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95532</t>
+          <t>96938</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>115250</t>
+          <t>115641</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>609475</t>
+          <t>609357</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>770310</t>
+          <t>762107</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>91,33%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>196501</t>
+          <t>197995</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>250608</t>
+          <t>250977</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>252851</t>
+          <t>251499</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>683761</t>
+          <t>635144</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>466138</t>
+          <t>466445</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1064859</t>
+          <t>1093781</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>54,4%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>781951</t>
+          <t>781582</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>836058</t>
+          <t>834564</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>294333</t>
+          <t>342950</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>725243</t>
+          <t>726595</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>945793</t>
+          <t>916871</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1544514</t>
+          <t>1544207</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,8%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86874</t>
+          <t>87400</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>123361</t>
+          <t>122813</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>218305</t>
+          <t>231596</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>346360</t>
+          <t>348234</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>337934</t>
+          <t>326609</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>446117</t>
+          <t>450374</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,3%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>350688</t>
+          <t>351236</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>387175</t>
+          <t>386649</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>74,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>492636</t>
+          <t>490762</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>620691</t>
+          <t>607400</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>866928</t>
+          <t>862671</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>975111</t>
+          <t>986436</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>75,13%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10308</t>
+          <t>9818</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40069</t>
+          <t>39461</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>253832</t>
+          <t>252209</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>227250</t>
+          <t>225329</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>281901</t>
+          <t>280252</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,99%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>200438</t>
+          <t>201046</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>230199</t>
+          <t>230689</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>506860</t>
+          <t>508483</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>719299</t>
+          <t>720948</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>773950</t>
+          <t>775871</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,49%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>461474</t>
+          <t>443169</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>656961</t>
+          <t>651149</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1051833</t>
+          <t>1043690</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1747210</t>
+          <t>1684771</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1607497</t>
+          <t>1574840</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2314020</t>
+          <t>2328210</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,53%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2713250</t>
+          <t>2719062</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2908737</t>
+          <t>2927042</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1826216</t>
+          <t>1888655</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2521593</t>
+          <t>2529736</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4629617</t>
+          <t>4615427</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5336140</t>
+          <t>5368797</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,32%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1413-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1413-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52942</t>
+          <t>52528</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84492</t>
+          <t>83265</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29287</t>
+          <t>28855</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53726</t>
+          <t>53227</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>87324</t>
+          <t>88026</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>126834</t>
+          <t>126121</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>389284</t>
+          <t>390511</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>420834</t>
+          <t>421248</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>252954</t>
+          <t>253453</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>277393</t>
+          <t>277825</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>653623</t>
+          <t>654336</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>693133</t>
+          <t>692431</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,72%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27147</t>
+          <t>26878</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49946</t>
+          <t>48668</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49180</t>
+          <t>50144</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>77671</t>
+          <t>78766</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>82598</t>
+          <t>83231</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119688</t>
+          <t>119895</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>316988</t>
+          <t>318266</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>339787</t>
+          <t>340056</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>294194</t>
+          <t>293099</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>322685</t>
+          <t>321721</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>619111</t>
+          <t>618904</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>656201</t>
+          <t>655568</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,73%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>84706</t>
+          <t>84020</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>122049</t>
+          <t>120991</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26337</t>
+          <t>26282</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48241</t>
+          <t>47083</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>116220</t>
+          <t>115956</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157461</t>
+          <t>156245</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>420340</t>
+          <t>421398</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>457683</t>
+          <t>458369</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,38%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>119541</t>
+          <t>120699</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>141445</t>
+          <t>141500</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>552710</t>
+          <t>553926</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>593951</t>
+          <t>594215</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,67%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>223906</t>
+          <t>226733</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>282438</t>
+          <t>282954</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>116810</t>
+          <t>118688</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>160424</t>
+          <t>159556</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>355575</t>
+          <t>356913</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>426062</t>
+          <t>423660</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>955896</t>
+          <t>955380</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1014428</t>
+          <t>1011601</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>553861</t>
+          <t>554729</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>597475</t>
+          <t>595597</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1526558</t>
+          <t>1528960</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1597045</t>
+          <t>1595707</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,72%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54348</t>
+          <t>52220</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>82625</t>
+          <t>80945</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>103514</t>
+          <t>101607</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142743</t>
+          <t>141719</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>165954</t>
+          <t>165577</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>216235</t>
+          <t>215399</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,43%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>267930</t>
+          <t>269610</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>296207</t>
+          <t>298335</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>426009</t>
+          <t>427033</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>465238</t>
+          <t>467145</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>703072</t>
+          <t>703908</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>753353</t>
+          <t>753730</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,99%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11384</t>
+          <t>12083</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>227550</t>
+          <t>226087</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>282573</t>
+          <t>281101</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>230949</t>
+          <t>229542</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>289298</t>
+          <t>286002</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,49%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>286817</t>
+          <t>286118</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>296248</t>
+          <t>296057</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>966187</t>
+          <t>967659</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1021210</t>
+          <t>1022673</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1257662</t>
+          <t>1260958</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1316011</t>
+          <t>1317418</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,16%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>490166</t>
+          <t>486113</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>574085</t>
+          <t>572233</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>605538</t>
+          <t>606835</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>698028</t>
+          <t>697865</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1115607</t>
+          <t>1117848</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1243162</t>
+          <t>1239993</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,65%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2696105</t>
+          <t>2697957</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2780024</t>
+          <t>2784077</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2680096</t>
+          <t>2680259</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2772586</t>
+          <t>2771289</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5405152</t>
+          <t>5408321</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5532707</t>
+          <t>5530466</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,19%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20704</t>
+          <t>20689</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42062</t>
+          <t>42215</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28784</t>
+          <t>27881</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54608</t>
+          <t>53993</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>54353</t>
+          <t>54415</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89795</t>
+          <t>87802</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>395149</t>
+          <t>394996</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>416507</t>
+          <t>416522</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>259846</t>
+          <t>260461</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285670</t>
+          <t>286573</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>661870</t>
+          <t>663863</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>697312</t>
+          <t>697250</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24450</t>
+          <t>24018</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48471</t>
+          <t>48794</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35522</t>
+          <t>35514</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61772</t>
+          <t>62632</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66457</t>
+          <t>65826</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102352</t>
+          <t>102396</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>370326</t>
+          <t>370003</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>394347</t>
+          <t>394779</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>276239</t>
+          <t>275379</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>302489</t>
+          <t>302497</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>654456</t>
+          <t>654412</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>690351</t>
+          <t>690982</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,3%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48978</t>
+          <t>48703</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81961</t>
+          <t>80193</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28702</t>
+          <t>28015</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52547</t>
+          <t>53111</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>86219</t>
+          <t>84250</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>124834</t>
+          <t>126424</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>547454</t>
+          <t>549222</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>580437</t>
+          <t>580712</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>207582</t>
+          <t>207018</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>231427</t>
+          <t>232114</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>764710</t>
+          <t>763120</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>803325</t>
+          <t>805294</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>107709</t>
+          <t>107326</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>151895</t>
+          <t>152921</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>104239</t>
+          <t>104290</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>146747</t>
+          <t>147203</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>224667</t>
+          <t>221621</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>283065</t>
+          <t>283063</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1007114</t>
+          <t>1006088</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1051300</t>
+          <t>1051683</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>617975</t>
+          <t>617519</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>660483</t>
+          <t>660432</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1640666</t>
+          <t>1640668</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1699064</t>
+          <t>1702110</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,48%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32852</t>
+          <t>32517</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58083</t>
+          <t>58797</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>154608</t>
+          <t>152048</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>201518</t>
+          <t>199690</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>192124</t>
+          <t>193597</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>248801</t>
+          <t>250388</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>452513</t>
+          <t>451799</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>477744</t>
+          <t>478079</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>558728</t>
+          <t>560556</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>605638</t>
+          <t>608198</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1022042</t>
+          <t>1020455</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1078719</t>
+          <t>1077246</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,77%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14426</t>
+          <t>15798</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>190323</t>
+          <t>190911</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>244135</t>
+          <t>245673</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>193149</t>
+          <t>196118</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>250311</t>
+          <t>250973</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,24%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>252456</t>
+          <t>251084</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264830</t>
+          <t>264811</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>865216</t>
+          <t>863678</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>919028</t>
+          <t>918440</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1125922</t>
+          <t>1125260</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1183084</t>
+          <t>1180115</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,75%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>275438</t>
+          <t>275511</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>344249</t>
+          <t>343623</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>601542</t>
+          <t>597421</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>688971</t>
+          <t>690951</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>891995</t>
+          <t>889414</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1010933</t>
+          <t>1011123</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3077661</t>
+          <t>3078287</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3146472</t>
+          <t>3146399</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2857944</t>
+          <t>2855964</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2945373</t>
+          <t>2949494</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5957892</t>
+          <t>5957702</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6076830</t>
+          <t>6079411</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>87,24%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23580</t>
+          <t>23522</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46263</t>
+          <t>48272</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17459</t>
+          <t>17661</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38084</t>
+          <t>38822</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46501</t>
+          <t>47971</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79158</t>
+          <t>77745</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>382829</t>
+          <t>380820</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>405512</t>
+          <t>405570</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>308971</t>
+          <t>308233</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>329596</t>
+          <t>329394</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>696989</t>
+          <t>698402</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>729646</t>
+          <t>728176</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,82%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13267</t>
+          <t>13843</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33392</t>
+          <t>32391</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33249</t>
+          <t>32654</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57877</t>
+          <t>57232</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50385</t>
+          <t>50155</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81932</t>
+          <t>83527</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>343835</t>
+          <t>344836</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>363960</t>
+          <t>363384</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>314396</t>
+          <t>315041</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>339024</t>
+          <t>339619</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>667568</t>
+          <t>665973</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>699115</t>
+          <t>699345</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,31%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29816</t>
+          <t>29250</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54571</t>
+          <t>55142</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24790</t>
+          <t>24450</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45526</t>
+          <t>46416</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60415</t>
+          <t>59037</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93979</t>
+          <t>92823</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>467343</t>
+          <t>466772</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>492098</t>
+          <t>492664</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>120597</t>
+          <t>119707</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>141333</t>
+          <t>141673</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>594057</t>
+          <t>595213</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>627621</t>
+          <t>628999</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,42%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86716</t>
+          <t>86580</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>124337</t>
+          <t>125729</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86148</t>
+          <t>88065</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>127419</t>
+          <t>127581</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>185482</t>
+          <t>187167</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>242337</t>
+          <t>243044</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,3%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1025301</t>
+          <t>1023909</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1062922</t>
+          <t>1063058</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>698457</t>
+          <t>698295</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>739728</t>
+          <t>737811</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1733177</t>
+          <t>1732470</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1790032</t>
+          <t>1788347</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>59686</t>
+          <t>59681</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>91494</t>
+          <t>92129</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>107734</t>
+          <t>107161</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>148837</t>
+          <t>150176</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>174490</t>
+          <t>178966</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>226375</t>
+          <t>230365</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>529212</t>
+          <t>528577</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>561020</t>
+          <t>561025</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>589407</t>
+          <t>588068</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>630510</t>
+          <t>631083</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1132575</t>
+          <t>1128585</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1184460</t>
+          <t>1179984</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>86,83%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>5693</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>126112</t>
+          <t>128131</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>173183</t>
+          <t>175329</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>129175</t>
+          <t>127575</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>178157</t>
+          <t>177477</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>280714</t>
+          <t>281452</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>908842</t>
+          <t>906696</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>955913</t>
+          <t>953894</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1191013</t>
+          <t>1191693</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1239995</t>
+          <t>1241595</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,68%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>247317</t>
+          <t>246709</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>312925</t>
+          <t>313096</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>444384</t>
+          <t>447767</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>535674</t>
+          <t>535297</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>710125</t>
+          <t>714764</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>823016</t>
+          <t>824035</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3072797</t>
+          <t>3072626</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3138405</t>
+          <t>3139013</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2995922</t>
+          <t>2996299</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3087212</t>
+          <t>3083829</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6094302</t>
+          <t>6093283</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6207193</t>
+          <t>6202554</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,67%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>73764</t>
+          <t>81795</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>59846</t>
+          <t>65425</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89794</t>
+          <t>98147</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>103718</t>
+          <t>114662</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>98122</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>121078</t>
+          <t>130986</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>177481</t>
+          <t>196457</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>155400</t>
+          <t>174474</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>198407</t>
+          <t>218772</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>430335</t>
+          <t>467639</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>414305</t>
+          <t>451287</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>444253</t>
+          <t>484009</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>343104</t>
+          <t>373058</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>325744</t>
+          <t>356734</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>356550</t>
+          <t>389598</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>773439</t>
+          <t>840697</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>752513</t>
+          <t>818382</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>795520</t>
+          <t>862680</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,18%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>504099</t>
+          <t>549434</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>504099</t>
+          <t>549434</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>504099</t>
+          <t>549434</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>446822</t>
+          <t>487720</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>446822</t>
+          <t>487720</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>446822</t>
+          <t>487720</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>950920</t>
+          <t>1037154</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>950920</t>
+          <t>1037154</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>950920</t>
+          <t>1037154</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>76731</t>
+          <t>80374</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62073</t>
+          <t>64977</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91770</t>
+          <t>98447</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>103836</t>
+          <t>118324</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89524</t>
+          <t>102467</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>119174</t>
+          <t>134532</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>180567</t>
+          <t>198698</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>159001</t>
+          <t>176941</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>202684</t>
+          <t>223547</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>374722</t>
+          <t>401947</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>359683</t>
+          <t>383874</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>389380</t>
+          <t>417344</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>278075</t>
+          <t>304168</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>262737</t>
+          <t>287960</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>292387</t>
+          <t>320025</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>652797</t>
+          <t>706114</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>630680</t>
+          <t>681265</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>674363</t>
+          <t>727871</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,44%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>451453</t>
+          <t>482321</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>451453</t>
+          <t>482321</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>451453</t>
+          <t>482321</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381911</t>
+          <t>422492</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>833364</t>
+          <t>904812</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>833364</t>
+          <t>904812</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>833364</t>
+          <t>904812</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>93044</t>
+          <t>102901</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36674</t>
+          <t>86256</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>156361</t>
+          <t>120761</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>61350</t>
+          <t>67845</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51270</t>
+          <t>57552</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69973</t>
+          <t>78281</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>154393</t>
+          <t>170746</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72349</t>
+          <t>150843</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>225099</t>
+          <t>191786</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>29,14%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>574501</t>
+          <t>367842</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>511184</t>
+          <t>349982</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>630871</t>
+          <t>384487</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>105561</t>
+          <t>119652</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>96938</t>
+          <t>109216</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>115641</t>
+          <t>129945</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>680063</t>
+          <t>487495</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>609357</t>
+          <t>466455</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>762107</t>
+          <t>507398</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>77,08%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>834456</t>
+          <t>658241</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>222363</t>
+          <t>237434</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>197995</t>
+          <t>211776</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>250977</t>
+          <t>265977</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>412223</t>
+          <t>234408</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>251499</t>
+          <t>213215</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>635144</t>
+          <t>257302</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>634585</t>
+          <t>471842</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>466445</t>
+          <t>437925</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1093781</t>
+          <t>506368</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>810196</t>
+          <t>891976</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>781582</t>
+          <t>863433</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>834564</t>
+          <t>917634</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>565871</t>
+          <t>626803</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>342950</t>
+          <t>603909</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>726595</t>
+          <t>647996</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1376067</t>
+          <t>1518779</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>916871</t>
+          <t>1484253</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1544207</t>
+          <t>1552696</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>78,0%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1032559</t>
+          <t>1129410</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1032559</t>
+          <t>1129410</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1032559</t>
+          <t>1129410</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2010652</t>
+          <t>1990621</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2010652</t>
+          <t>1990621</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2010652</t>
+          <t>1990621</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>104202</t>
+          <t>118464</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>87400</t>
+          <t>100285</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>122813</t>
+          <t>141315</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>302386</t>
+          <t>329782</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>231596</t>
+          <t>304668</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>348234</t>
+          <t>351879</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>406588</t>
+          <t>448246</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>326609</t>
+          <t>418299</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>450374</t>
+          <t>482892</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,56%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>369847</t>
+          <t>448512</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>351236</t>
+          <t>425661</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>386649</t>
+          <t>466691</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>536610</t>
+          <t>500345</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>490762</t>
+          <t>478248</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>607400</t>
+          <t>525459</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>906457</t>
+          <t>948857</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>862671</t>
+          <t>914211</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>986436</t>
+          <t>978804</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>70,06%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1313045</t>
+          <t>1397103</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>21102</t>
+          <t>20592</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9818</t>
+          <t>10890</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39461</t>
+          <t>37113</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>230092</t>
+          <t>253661</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>209148</t>
+          <t>230614</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>252209</t>
+          <t>276753</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>251195</t>
+          <t>274254</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>225329</t>
+          <t>248057</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>280252</t>
+          <t>306874</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,39%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>219405</t>
+          <t>216636</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>201046</t>
+          <t>200115</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>230689</t>
+          <t>226338</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>530600</t>
+          <t>589935</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>508483</t>
+          <t>566843</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>551544</t>
+          <t>612982</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>750005</t>
+          <t>806570</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>720948</t>
+          <t>773950</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>775871</t>
+          <t>832767</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,05%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>591205</t>
+          <t>641561</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>443169</t>
+          <t>599590</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>651149</t>
+          <t>690038</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1213605</t>
+          <t>1118682</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1043690</t>
+          <t>1072953</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1684771</t>
+          <t>1167123</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1804810</t>
+          <t>1760243</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1574840</t>
+          <t>1695368</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2328210</t>
+          <t>1829955</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>25,89%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2779006</t>
+          <t>2794551</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2719062</t>
+          <t>2746074</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2927042</t>
+          <t>2836522</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2359821</t>
+          <t>2513961</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1888655</t>
+          <t>2465520</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2529736</t>
+          <t>2559690</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5138827</t>
+          <t>5308512</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4615427</t>
+          <t>5238800</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5368797</t>
+          <t>5373387</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>76,02%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3370211</t>
+          <t>3436112</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3370211</t>
+          <t>3436112</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3370211</t>
+          <t>3436112</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3573426</t>
+          <t>3632643</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3573426</t>
+          <t>3632643</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3573426</t>
+          <t>3632643</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6943637</t>
+          <t>7068755</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6943637</t>
+          <t>7068755</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6943637</t>
+          <t>7068755</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
